--- a/results/metrics_modelling2_filtered_optuna.xlsx
+++ b/results/metrics_modelling2_filtered_optuna.xlsx
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.85</v>
       </c>
       <c r="H34" t="n">
         <v>0.85</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9068181818181819</v>
+        <v>0.8977272727272728</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -1685,19 +1685,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="H35" t="n">
         <v>0.9</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.9045454545454544</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8260869565217392</v>
+        <v>0.8780487804878048</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="H36" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9113636363636364</v>
+        <v>0.9227272727272726</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -1799,19 +1799,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.88</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="H38" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.8454545454545455</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -2027,19 +2027,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8</v>
       </c>
       <c r="H44" t="n">
         <v>0.8</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8727272727272728</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -2144,16 +2144,16 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.9068181818181819</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -2220,16 +2220,16 @@
         <v>0.88</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9072164948453607</v>
+        <v>0.9052631578947369</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8657407407407407</v>
+        <v>0.8738425925925927</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -2331,19 +2331,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.88</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.9183673469387755</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.9</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8738425925925927</v>
+        <v>0.8761574074074074</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.88</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.8576388888888888</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.9</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="H55" t="n">
         <v>0.9375</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8206018518518519</v>
+        <v>0.8391203703703703</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2483,19 +2483,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8910891089108911</v>
+        <v>0.9</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="H56" t="n">
         <v>0.9375</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8206018518518519</v>
+        <v>0.8391203703703703</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -2597,19 +2597,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.8737864077669902</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="H59" t="n">
         <v>0.9375</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7650462962962963</v>
+        <v>0.7835648148148149</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8627450980392157</v>
       </c>
       <c r="H60" t="n">
         <v>0.9166666666666666</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8101851851851851</v>
+        <v>0.8287037037037036</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>

--- a/results/metrics_modelling2_filtered_optuna.xlsx
+++ b/results/metrics_modelling2_filtered_optuna.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.92</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="H34" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8977272727272728</v>
+        <v>0.9318181818181818</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -1688,16 +1688,16 @@
         <v>0.9066666666666666</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9045454545454544</v>
+        <v>0.8886363636363637</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8780487804878048</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="H36" t="n">
         <v>0.9</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9227272727272726</v>
+        <v>0.9136363636363636</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -1761,19 +1761,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.85</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.85</v>
       </c>
       <c r="H37" t="n">
         <v>0.85</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9159090909090909</v>
+        <v>0.8977272727272728</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -1799,19 +1799,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F38" t="n">
-        <v>0.761904761904762</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8454545454545455</v>
+        <v>0.8045454545454546</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F39" t="n">
-        <v>0.761904761904762</v>
+        <v>0.6829268292682926</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8454545454545455</v>
+        <v>0.7863636363636364</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.92</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.8977272727272728</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -1913,19 +1913,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.88</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7906976744186046</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="H41" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8704545454545455</v>
+        <v>0.7704545454545453</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_onehot</t>
+          <t>logisticregression_net_impact_ordenc</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.68</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="H42" t="n">
         <v>0.85</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9159090909090909</v>
+        <v>0.8068181818181819</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8</v>
       </c>
       <c r="H43" t="n">
         <v>0.8</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8727272727272728</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2061,23 +2061,23 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>logisticregression_net_impact_ordenc</t>
+          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.92</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.85</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.85</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8727272727272728</v>
+        <v>0.8977272727272728</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
@@ -2089,33 +2089,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_net_impact_ordenc</t>
+          <t>kneighborsclassifier_smote_splashing_ordenc</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.86</v>
       </c>
       <c r="H46" t="n">
-        <v>0.85</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I46" t="n">
-        <v>0.9159090909090909</v>
+        <v>0.8182870370370371</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -2127,33 +2127,33 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>xgbclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.811881188118812</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="H47" t="n">
-        <v>0.85</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9068181818181819</v>
+        <v>0.704861111111111</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -2165,33 +2165,33 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>net_impact</t>
+          <t>splashing</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>svc_smote_net_impact_ordenc</t>
+          <t>kneighborsclassifier_splashing_ordenc</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.7997685185185186</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2213,23 +2213,23 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_smote_splashing_ordenc</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="E49" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.8979591836734694</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.88</v>
       </c>
-      <c r="F49" t="n">
-        <v>0.9052631578947369</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.9148936170212766</v>
-      </c>
       <c r="H49" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8738425925925927</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2251,23 +2251,23 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>xgbclassifier_smote_splashing</t>
+          <t>kneighborsclassifier_splashing_ordenc</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8490566037735848</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7758620689655172</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I50" t="n">
-        <v>0.7280092592592593</v>
+        <v>0.7997685185185186</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2289,23 +2289,23 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>catboostclassifier_smote_splashing</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.88</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9052631578947369</v>
+        <v>0.9</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.8653846153846154</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9375</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8738425925925927</v>
+        <v>0.8391203703703703</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2327,23 +2327,23 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9</v>
+        <v>0.8490566037735849</v>
       </c>
       <c r="H52" t="n">
         <v>0.9375</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8761574074074074</v>
+        <v>0.8206018518518519</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -2365,23 +2365,23 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>kneighborsclassifier_splashing_ordenc</t>
+          <t>catboostclassifier_splashing</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9072164948453607</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9375</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8657407407407407</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2403,23 +2403,23 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>catboostclassifier_smote_splashing</t>
+          <t>xgbclassifier_ohe_smote_splashing</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.7884615384615384</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9375</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8576388888888888</v>
+        <v>0.7233796296296295</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -2441,23 +2441,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.7812500000000001</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2479,23 +2479,23 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>catboostclassifier_splashing</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8653846153846154</v>
+        <v>0.8431372549019608</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9375</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8391203703703703</v>
+        <v>0.7997685185185186</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2517,23 +2517,23 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="G57" t="n">
-        <v>0.92</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9050925925925927</v>
+        <v>0.7789351851851851</v>
       </c>
       <c r="J57" t="n">
         <v>1</v>
@@ -2555,23 +2555,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_onehot</t>
+          <t>logisticregression_splashing_onehot</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.92</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9050925925925927</v>
+        <v>0.8101851851851851</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
@@ -2588,28 +2588,28 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>xgbclassifier_ohe_smote_splashing</t>
+          <t>svc_smote_net_impact_onehot_linear</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8737864077669902</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9375</v>
+        <v>0.85</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7835648148148149</v>
+        <v>0.8613636363636364</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -2626,28 +2626,28 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>svc_smote_net_impact_ordenc_linear</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F60" t="n">
-        <v>0.888888888888889</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="H60" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8287037037037036</v>
+        <v>0.8454545454545455</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -2659,33 +2659,33 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>splashing</t>
+          <t>net_impact</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>svc_smote_net_impact_ordenc_linear</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.92</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9131944444444444</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2707,23 +2707,23 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>svc_smote_splashing_ordenc</t>
+          <t>svc_smote_splashing_onehot_linear</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.854368932038835</v>
       </c>
       <c r="G62" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9050925925925927</v>
+        <v>0.7546296296296295</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity</t>
+          <t>df_modelling_dimensionless_pf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2745,23 +2745,23 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>svc_smote_splashing_onehot_linear</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8</v>
       </c>
       <c r="F63" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8514851485148515</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8287037037037036</v>
+        <v>0.7627314814814815</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>df_modelling_no_multicollinearity_pf</t>
+          <t>df_modelling_dimensionless</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2783,23 +2783,23 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>svc_smote_splashing_ordenc_linear</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.8571428571428572</v>
       </c>
       <c r="G64" t="n">
-        <v>0.88</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="H64" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9375</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8472222222222222</v>
+        <v>0.7465277777777777</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>df_modelling_dimensionless_pf</t>
+          <t>df_modelling_no_multicollinearity_pf</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2821,25 +2821,291 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>logisticregression_splashing_onehot</t>
+          <t>svc_smote_splashing_ordenc_linear</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.854368932038835</v>
       </c>
       <c r="G65" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8</v>
       </c>
       <c r="H65" t="n">
         <v>0.9166666666666666</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8101851851851851</v>
+        <v>0.7546296296296295</v>
       </c>
       <c r="J65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_onehot_poly</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.7733333333333333</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc_poly</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>net_impact</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>svc_smote_net_impact_ordenc_poly</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.7477272727272728</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot_poly</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.795138888888889</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless_pf</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_onehot_poly</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.8514851485148515</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.8113207547169812</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.7627314814814815</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>df_modelling_dimensionless</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc_poly</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8738425925925927</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>df_modelling_no_multicollinearity_pf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>svc_smote_splashing_ordenc_poly</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8182870370370371</v>
+      </c>
+      <c r="J72" t="n">
         <v>1</v>
       </c>
     </row>
